--- a/templates/Files.xlsx
+++ b/templates/Files.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/w.f.oudijk/Documents/ERDERA/projects-erdera/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9685A5F6-07D3-DA49-B964-F821254A122F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5797917B-7FBF-354F-B62E-4250F4D2C80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,81 +140,18 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color rgb="FF000000"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">The determination of complete (typically
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">nucleotide) sequences, including those
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">of genomes (full genome sequencing, de
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">novo sequencing and resequencing),
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">amplicons and transcriptomes. In FAIR
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Genomes: Sequencing. Ideally:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">SequencingRuns.
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> Select one item from Experiments</t>
+          <t>The determination of complete (typically
+nucleotide) sequences, including those
+of genomes (full genome sequencing, de
+novo sequencing and resequencing),
+amplicons and transcriptomes. In FAIR
+Genomes: Sequencing. Ideally:
+SequencingRuns.
+ Select one item from Experiments</t>
         </r>
       </text>
     </comment>
@@ -223,31 +160,13 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color rgb="FF000000"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">A fixed-size datum calculated (by using
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">a hash function) for a file
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> STRING</t>
+          <t>A fixed-size datum calculated (by using
+a hash function) for a file
+ STRING</t>
         </r>
       </text>
     </comment>
@@ -300,7 +219,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>id</t>
   </si>
@@ -329,214 +248,55 @@
     <t>Organisations</t>
   </si>
   <si>
-    <t>Aalborg University</t>
+    <t>acu-alanay</t>
   </si>
   <si>
-    <t>Aarhus University</t>
+    <t>Acıbadem Adana Hospital</t>
   </si>
   <si>
-    <t>Aarhus University Hospital</t>
+    <t>aous-renieri</t>
   </si>
   <si>
-    <t>Accare</t>
+    <t>Centogene (Germany)</t>
   </si>
   <si>
-    <t>Agencia Española de Medicamentos y Productos Sanitarios</t>
+    <t>centogene-bauer</t>
   </si>
   <si>
-    <t>Agenzia Regionale di Sanità della Toscana</t>
+    <t>cheo-lochmuller</t>
   </si>
   <si>
-    <t>Agostino Gemelli University Polyclinic</t>
+    <t>Children's Hospital of Eastern Ontario</t>
   </si>
   <si>
-    <t>Alexander Monro Ziekenhuis</t>
-  </si>
-  <si>
-    <t>Allegheny Health Network</t>
-  </si>
-  <si>
-    <t>Alrijne Ziekenhuis</t>
-  </si>
-  <si>
-    <t>Amsterdam UMC Location University of Amsterdam</t>
-  </si>
-  <si>
-    <t>Amsterdam UMC Location Vrije Universiteit Amsterdam</t>
-  </si>
-  <si>
-    <t>Amsterdam University Medical Centers</t>
-  </si>
-  <si>
-    <t>Antaros Medical (Sweden)</t>
-  </si>
-  <si>
-    <t>Antonius Ziekenhuis</t>
-  </si>
-  <si>
-    <t>Antwerp University Hospital</t>
-  </si>
-  <si>
-    <t>Austin Health</t>
-  </si>
-  <si>
-    <t>Azienda Ospedale - Università Padova</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliera Citta' della Salute e della Scienza di Torino</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliera San Camillo-Forlanini</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliera San Gerardo</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliera Universitaria Integrata Verona</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliera Universitaria Pisana</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliera Universitaria Senese</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliero-Universitaria Careggi</t>
-  </si>
-  <si>
-    <t>Azienda Ospedaliero-Universitaria di Modena</t>
-  </si>
-  <si>
-    <t>Azienda Sanitaria Unità Locale di Reggio Emilia</t>
-  </si>
-  <si>
-    <t>Azienda Socio Sanitaria Territoriale degli Spedali Civili di Brescia</t>
-  </si>
-  <si>
-    <t>Azienda USL di Bologna</t>
-  </si>
-  <si>
-    <t>Azienda Usl Toscana Centro</t>
-  </si>
-  <si>
-    <t>Bambino Gesù Children's Hospital</t>
-  </si>
-  <si>
-    <t>Barcelona Institute for Global Health</t>
-  </si>
-  <si>
-    <t>Barcelona Supercomputing Center</t>
-  </si>
-  <si>
-    <t>Bayer (Germany)</t>
-  </si>
-  <si>
-    <t>Bicêtre Hospital</t>
-  </si>
-  <si>
-    <t>Biobanking and Biomolecular Resources Research Infrastructure Consortium</t>
-  </si>
-  <si>
-    <t>Bradford Royal Infirmary</t>
-  </si>
-  <si>
-    <t>Bravis Ziekenhuis</t>
-  </si>
-  <si>
-    <t>Cambridge University Hospitals NHS Foundation Trust</t>
-  </si>
-  <si>
-    <t>Capital Region of Denmark</t>
-  </si>
-  <si>
-    <t>Casa Sollievo della Sofferenza</t>
-  </si>
-  <si>
-    <t>Catharina Ziekenhuis</t>
-  </si>
-  <si>
-    <t>Celltrion (South Korea)</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier de Luxembourg</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Universitaire de Bordeaux</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Universitaire de Lille</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Universitaire de Montpellier</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Universitaire de Nice</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Universitaire de Rennes</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Universitaire de Toulouse</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Universitaire Henri-Mondor</t>
-  </si>
-  <si>
-    <t>Centro Hospitalar de Lisboa Central</t>
-  </si>
-  <si>
-    <t>Centro Hospitalar do Porto</t>
-  </si>
-  <si>
-    <t>Centro Hospitalar Lisboa Norte</t>
-  </si>
-  <si>
-    <t>Charité - Universitätsmedizin Berlin</t>
-  </si>
-  <si>
-    <t>Chiesi (Italy)</t>
-  </si>
-  <si>
-    <t>Children's Clinical University Hospital</t>
-  </si>
-  <si>
-    <t>Children's Health Ireland at Crumlin</t>
-  </si>
-  <si>
-    <t>Children's Hospital Agia Sophia</t>
-  </si>
-  <si>
-    <t>Children's Hospital Zagreb</t>
-  </si>
-  <si>
-    <t>Children's Memorial Health Institute</t>
+    <t>chm-guerrini</t>
   </si>
   <si>
     <t>CHU Dijon Bourgogne</t>
   </si>
   <si>
-    <t>Clinical Emergency Hospital Bucharest</t>
+    <t>chud-faivre</t>
   </si>
   <si>
-    <t>Cliniques Universitaires Saint-Luc</t>
+    <t>cuni-macek</t>
   </si>
   <si>
-    <t>Cyprus Institute of Neurology and Genetics</t>
+    <t>cusl-cilio</t>
   </si>
   <si>
-    <t>Diakonessenhuis hospital</t>
+    <t>Eginition Hospital</t>
   </si>
   <si>
-    <t>Duke Institute for Health Innovation</t>
+    <t>ekut-haack</t>
   </si>
   <si>
-    <t>Dutch Initiative on Crohn and Colitis</t>
+    <t>ekut-lerche</t>
   </si>
   <si>
-    <t>Düsseldorf University Hospital</t>
+    <t>ekut-schoels</t>
   </si>
   <si>
-    <t>EB House Austria</t>
+    <t>Endo-ERN</t>
   </si>
   <si>
     <t>Erasmus Hospital</t>
@@ -545,787 +305,268 @@
     <t>Erasmus MC</t>
   </si>
   <si>
-    <t>Erasmus University Rotterdam</t>
+    <t>ERKNet</t>
   </si>
   <si>
-    <t>Essen University Hospital</t>
+    <t>ERN BOND</t>
   </si>
   <si>
-    <t>European Bioinformatics Institute</t>
+    <t>ERN CRANIO</t>
   </si>
   <si>
-    <t>European Research and Project Office</t>
+    <t>ERN EpiCARE</t>
   </si>
   <si>
-    <t>Fakultní nemocnice Bulovka</t>
+    <t>ERN EURACAN</t>
   </si>
   <si>
-    <t>Federico II University Hospital</t>
+    <t>ERN EURO-NMD</t>
   </si>
   <si>
-    <t>Finnish Institute for Health and Welfare</t>
+    <t>ERN EuroBloodNet</t>
   </si>
   <si>
-    <t>Fondation Saint-Luc</t>
+    <t>ERN eUROGEN</t>
   </si>
   <si>
-    <t>Fondazione IRCCS Ca' Granda Ospedale Maggiore Policlinico</t>
+    <t>ERN EYE</t>
   </si>
   <si>
-    <t>Fondazione IRCCS Istituto Nazionale dei Tumori</t>
+    <t>ERN GENTURIS</t>
   </si>
   <si>
-    <t>Fondazione IRCCS Istituto Neurologico Carlo Besta</t>
+    <t>ERN GUARD-Heart</t>
   </si>
   <si>
-    <t>Frisius MC</t>
+    <t>ERN ITHACA</t>
   </si>
   <si>
-    <t>Fundación para el Fomento de la Investigación Sanitaria y Biomédica de la Comunitat Valenciana</t>
+    <t>ERN LUNG</t>
   </si>
   <si>
-    <t>Gdańsk Medical University</t>
+    <t>ERN PaedCan</t>
   </si>
   <si>
-    <t>Gelre Hospitals</t>
+    <t>ERN RARE-LIVER</t>
   </si>
   <si>
-    <t>GGZ Drenthe</t>
+    <t>ERN ReCONNET</t>
   </si>
   <si>
-    <t>GGZ Friesland</t>
+    <t>ERN RITA</t>
+  </si>
+  <si>
+    <t>ERN Skin</t>
+  </si>
+  <si>
+    <t>ERN TRANSPLANT-CHILD</t>
+  </si>
+  <si>
+    <t>ERN-RND</t>
+  </si>
+  <si>
+    <t>ERNICA</t>
+  </si>
+  <si>
+    <t>eur-barakat</t>
   </si>
   <si>
     <t>Ghent University</t>
   </si>
   <si>
-    <t>Ghent University Hospital</t>
+    <t>Hospital Universitario Son Espases</t>
   </si>
   <si>
-    <t>GlaxoSmithKline (United Kingdom)</t>
+    <t>huvh-colobran</t>
   </si>
   <si>
-    <t>Guy's and St Thomas' NHS Foundation Trust</t>
+    <t>huvh-tizzano</t>
   </si>
   <si>
-    <t>Haga Hospital</t>
+    <t>igcz-plawski</t>
   </si>
   <si>
-    <t>Hanze University of Applied Sciences</t>
+    <t>iierspainudp-bermejo</t>
   </si>
   <si>
-    <t>Hasselt University</t>
+    <t>Institute of Human Genetics</t>
   </si>
   <si>
-    <t>Haukeland University Hospital</t>
+    <t>Institute of Pathology and Genetics</t>
   </si>
   <si>
-    <t>Health-RI</t>
+    <t>Instituto de Salud Carlos III</t>
   </si>
   <si>
-    <t>Heidelberg Institute of Global Health</t>
+    <t>ipg-dahan</t>
   </si>
   <si>
-    <t>Helmholtz Zentrum München</t>
+    <t>Izmir Biomedicine and Genome Center</t>
   </si>
   <si>
-    <t>Helsinki University Hospital</t>
-  </si>
-  <si>
-    <t>Herzzentrum Dresden Universitaetsklinik</t>
-  </si>
-  <si>
-    <t>Hospices Civils de Lyon</t>
-  </si>
-  <si>
-    <t>Hospital Clínic de Barcelona</t>
-  </si>
-  <si>
-    <t>Hospital da Luz</t>
-  </si>
-  <si>
-    <t>Hospital de São João</t>
-  </si>
-  <si>
-    <t>Hospital La Paz Institute for Health Research</t>
-  </si>
-  <si>
-    <t>Hospital Sant Joan de Déu Barcelona</t>
-  </si>
-  <si>
-    <t>Hospital Universitari Germans Trias i Pujol</t>
-  </si>
-  <si>
-    <t>Hospital Universitario 12 De Octubre</t>
-  </si>
-  <si>
-    <t>HuisartsenOrganisatie Oost-Gelderland</t>
-  </si>
-  <si>
-    <t>Huisartsenpraktijk Meander</t>
-  </si>
-  <si>
-    <t>Hôpital Charles-Nicolle</t>
-  </si>
-  <si>
-    <t>Hôpital Cochin</t>
-  </si>
-  <si>
-    <t>Hôpital de la Timone</t>
-  </si>
-  <si>
-    <t>Hôpital Femme Mère Enfant</t>
-  </si>
-  <si>
-    <t>Hôpital Jeanne de Flandre</t>
-  </si>
-  <si>
-    <t>Hôpital Necker-Enfants Malades</t>
-  </si>
-  <si>
-    <t>Hôpital Raymond-Poincaré</t>
-  </si>
-  <si>
-    <t>Hôpital Robert-Debré</t>
-  </si>
-  <si>
-    <t>Hôpitaux Universitaires de Strasbourg</t>
-  </si>
-  <si>
-    <t>Hôpitaux Universitaires Henri-Mondor</t>
-  </si>
-  <si>
-    <t>i3S - Instituto de Investigação e Inovação em Saúde, Universidade do Porto</t>
-  </si>
-  <si>
-    <t>Icahn School of Medicine at Mount Sinai</t>
-  </si>
-  <si>
-    <t>IJsselland Ziekenhuis</t>
-  </si>
-  <si>
-    <t>ImaginAb (United States)</t>
-  </si>
-  <si>
-    <t>Imperial College London</t>
-  </si>
-  <si>
-    <t>Innsbruck Medical University</t>
-  </si>
-  <si>
-    <t>Inserm</t>
-  </si>
-  <si>
-    <t>Institut Curie</t>
-  </si>
-  <si>
-    <t>Institut Jules Bordet</t>
-  </si>
-  <si>
-    <t>Institut Universitari d'Investigació en Atenció Primària Jordi Gol</t>
-  </si>
-  <si>
-    <t>Institute for Experimental Endocrinology and Oncology</t>
-  </si>
-  <si>
-    <t>Institute of Molecular and Translational Medicine</t>
-  </si>
-  <si>
-    <t>Institute of Oncology Ljubljana</t>
-  </si>
-  <si>
-    <t>Institute of Rheumatology</t>
-  </si>
-  <si>
-    <t>Instituto Português de Oncologia Francisco Gentil</t>
-  </si>
-  <si>
-    <t>IPO Porto</t>
-  </si>
-  <si>
-    <t>IRCCS Azienda Ospedliero-Universitaria di Bologna Policlinico di Sant'Orsola</t>
-  </si>
-  <si>
-    <t>Isala</t>
-  </si>
-  <si>
-    <t>Istituti Clinici Scientifici Maugeri</t>
-  </si>
-  <si>
-    <t>Istituto Dermopatico dell'Immacolata</t>
-  </si>
-  <si>
-    <t>Istituto di Fisiologia Clinica</t>
-  </si>
-  <si>
-    <t>Istituto di Ricovero e Cura a Carattere Scientifico San Raffaele</t>
-  </si>
-  <si>
-    <t>Istituto Giannina Gaslini</t>
-  </si>
-  <si>
-    <t>Istituto Nazionale di Fisica Nucleare, Sezione di Padova</t>
-  </si>
-  <si>
-    <t>Istituto Neurologico Mediterraneo</t>
-  </si>
-  <si>
-    <t>Istituto Ortopedico Gaetano Pini</t>
-  </si>
-  <si>
-    <t>Jackson Laboratory</t>
-  </si>
-  <si>
-    <t>Janssen (Belgium)</t>
-  </si>
-  <si>
-    <t>Karolinska Institutet</t>
-  </si>
-  <si>
-    <t>Karolinska University Hospital</t>
-  </si>
-  <si>
-    <t>Kerckhoff Klinik</t>
-  </si>
-  <si>
-    <t>Knowledge Centre for Sport Netherlands</t>
-  </si>
-  <si>
-    <t>Krankenhaus Bethanien</t>
+    <t>kimg-maver</t>
   </si>
   <si>
     <t>KU Leuven</t>
   </si>
   <si>
-    <t>Laiko General Hospital of Athens</t>
+    <t>Latvian Biomedical Research and Study Centre</t>
   </si>
   <si>
-    <t>Leibniz Institute for Prevention Research and Epidemiology - BIPS</t>
-  </si>
-  <si>
-    <t>Leiden University</t>
+    <t>lbmc-inaskina</t>
   </si>
   <si>
     <t>Leiden University Medical Center</t>
   </si>
   <si>
-    <t>Lentis</t>
+    <t>lumc-santen</t>
   </si>
   <si>
-    <t>Lifelines</t>
+    <t>Medical University of Sofia</t>
   </si>
   <si>
-    <t>Lithuanian University of Health Sciences</t>
-  </si>
-  <si>
-    <t>Ljubljana University Medical Centre</t>
-  </si>
-  <si>
-    <t>LMU Klinikum</t>
-  </si>
-  <si>
-    <t>London School of Hygiene &amp; Tropical Medicine</t>
-  </si>
-  <si>
-    <t>Ludger (United Kingdom)</t>
-  </si>
-  <si>
-    <t>Lygature</t>
-  </si>
-  <si>
-    <t>Maastricht University</t>
-  </si>
-  <si>
-    <t>Maastricht University Medical Centre</t>
-  </si>
-  <si>
-    <t>Manchester University NHS Foundation Trust</t>
-  </si>
-  <si>
-    <t>Martini Ziekenhuis</t>
-  </si>
-  <si>
-    <t>Masaryk Memorial Cancer Institute</t>
-  </si>
-  <si>
-    <t>Mater Dei Hospital</t>
-  </si>
-  <si>
-    <t>Mater Misericordiae University Hospital</t>
-  </si>
-  <si>
-    <t>Meander Medisch Centrum</t>
-  </si>
-  <si>
-    <t>Medical College of Wisconsin</t>
-  </si>
-  <si>
-    <t>Medical Genetics Center</t>
-  </si>
-  <si>
-    <t>Medical University of Vienna</t>
-  </si>
-  <si>
-    <t>Medisch Centrum Leeuwarden</t>
-  </si>
-  <si>
-    <t>Medisch Spectrum Twente</t>
-  </si>
-  <si>
-    <t>Medizinische Hochschule Hannover</t>
+    <t>MetabERN</t>
   </si>
   <si>
     <t>Meyer Children's Hospital</t>
   </si>
   <si>
-    <t>Máxima Medisch Centrum</t>
+    <t>mus-kaneva</t>
   </si>
   <si>
-    <t>National Institute for Public Health and the Environment</t>
+    <t>Newcastle University</t>
   </si>
   <si>
-    <t>National Institute of Cardiovascular Diseases</t>
+    <t>nkua-karadima</t>
   </si>
   <si>
-    <t>National Institute of Geriatrics, Rheumatology and Rehabilitation</t>
-  </si>
-  <si>
-    <t>National Medical Institute of the Ministry of Interior and Administration</t>
-  </si>
-  <si>
-    <t>Netherlands Comprehensive Cancer Organisation</t>
-  </si>
-  <si>
-    <t>Netherlands Organisation for Applied Scientific Research</t>
-  </si>
-  <si>
-    <t>Netherlands Pharmacovigilance Centre Lareb</t>
-  </si>
-  <si>
-    <t>Northumbria University</t>
-  </si>
-  <si>
-    <t>Norwegian Institute of Public Health</t>
-  </si>
-  <si>
-    <t>Norwegian University of Science and Technology</t>
-  </si>
-  <si>
-    <t>Novartis (Netherlands)</t>
-  </si>
-  <si>
-    <t>Odense University Hospital</t>
-  </si>
-  <si>
-    <t>Ommelander Ziekenhuis Groningen</t>
-  </si>
-  <si>
-    <t>Oslo University Hospital</t>
-  </si>
-  <si>
-    <t>Ospedale di Parma</t>
-  </si>
-  <si>
-    <t>Ospedale Policlinico San Martino</t>
-  </si>
-  <si>
-    <t>Ospedale Sacro Cuore Don Calabria</t>
-  </si>
-  <si>
-    <t>Ospedale San Bortolo</t>
-  </si>
-  <si>
-    <t>Ospedale San Giovanni Bosco</t>
-  </si>
-  <si>
-    <t>Ospedale San Paolo</t>
-  </si>
-  <si>
-    <t>Ospedali Riuniti di Ancona</t>
-  </si>
-  <si>
-    <t>Ospedali Riuniti San Giovanni di Dio e Ruggi d'Aragona</t>
-  </si>
-  <si>
-    <t>Otto-von-Guericke University Magdeburg</t>
-  </si>
-  <si>
-    <t>Oulu University Hospital</t>
-  </si>
-  <si>
-    <t>Parkinson Platform Noord Nederland</t>
-  </si>
-  <si>
-    <t>Parnassia Groep</t>
-  </si>
-  <si>
-    <t>Pauls Stradiņš Clinical University Hospital</t>
-  </si>
-  <si>
-    <t>Pfizer (United Kingdom)</t>
-  </si>
-  <si>
-    <t>Pharmo Institute</t>
-  </si>
-  <si>
-    <t>Piedmont Reference Center for Epidemiology and Cancer Prevention</t>
-  </si>
-  <si>
-    <t>Pitié-Salpêtrière Hospital</t>
-  </si>
-  <si>
-    <t>Policlinico Umberto I</t>
-  </si>
-  <si>
-    <t>Pomeranian Medical University</t>
-  </si>
-  <si>
-    <t>Princess Margaret Cancer Centre</t>
-  </si>
-  <si>
-    <t>Princess Máxima Center</t>
+    <t>nkua-makrythanasis</t>
   </si>
   <si>
     <t>Radboud University Medical Center</t>
   </si>
   <si>
-    <t>Radiotherapeutisch Instituut Friesland</t>
+    <t>rakus-lace</t>
   </si>
   <si>
-    <t>Radiotherapiegroep</t>
+    <t>rcsi-byrne</t>
   </si>
   <si>
-    <t>RECETOX</t>
+    <t>rcsi-conlon</t>
   </si>
   <si>
-    <t>Riga Stradiņš University</t>
+    <t>rcsi-delanty</t>
   </si>
   <si>
-    <t>Rigshospitalet</t>
+    <t>rcsi-hurley</t>
   </si>
   <si>
-    <t>Roche (Switzerland)</t>
+    <t>Riga East University Hospital</t>
   </si>
   <si>
-    <t>Royal Marsden Hospital</t>
+    <t>Royal College of Surgeons in Ireland</t>
   </si>
   <si>
-    <t>Sahlgrenska University Hospital</t>
+    <t>rumc-devoer</t>
   </si>
   <si>
-    <t>Sanofi (France)</t>
+    <t>rumc-vissers</t>
   </si>
   <si>
-    <t>Semmelweis University</t>
+    <t>St. Anna Children's Cancer Research Institute</t>
   </si>
   <si>
-    <t>Serviço Nacional de Saúde</t>
+    <t>Technical University of Munich</t>
   </si>
   <si>
-    <t>Siemens (Netherlands)</t>
+    <t>tigem-nigro</t>
   </si>
   <si>
-    <t>Spaarne Gasthuis</t>
+    <t>tuh-kounap</t>
   </si>
   <si>
-    <t>Spitalul Clinic Colentina</t>
+    <t>ucam-horvath</t>
   </si>
   <si>
-    <t>St. Anne's University Hospital Brno</t>
+    <t>UDN-Italy</t>
   </si>
   <si>
-    <t>St. Antonius Ziekenhuis</t>
+    <t>UDN-Spain</t>
   </si>
   <si>
-    <t>Statens Serum Institut</t>
+    <t>ukhd-hempel</t>
   </si>
   <si>
-    <t>Städtisches Klinikum Dessau</t>
+    <t>unew-topf</t>
   </si>
   <si>
-    <t>Sunnybrook Hospital</t>
-  </si>
-  <si>
-    <t>Swansea University</t>
-  </si>
-  <si>
-    <t>Synaeda Psycho Medisch Centrum</t>
-  </si>
-  <si>
-    <t>Takeda (Japan)</t>
-  </si>
-  <si>
-    <t>Takeda (United Kingdom)</t>
-  </si>
-  <si>
-    <t>Tampere University</t>
-  </si>
-  <si>
-    <t>Tartu University Hospital</t>
-  </si>
-  <si>
-    <t>Temple Street Children's University Hospital</t>
-  </si>
-  <si>
-    <t>Tergooi</t>
-  </si>
-  <si>
-    <t>The Christie Hospital</t>
-  </si>
-  <si>
-    <t>The Netherlands Cancer Institute</t>
-  </si>
-  <si>
-    <t>The University of Texas MD Anderson Cancer Center</t>
-  </si>
-  <si>
-    <t>The University of Western Australia</t>
-  </si>
-  <si>
-    <t>Tjongerschans</t>
-  </si>
-  <si>
-    <t>Treant Zorggroep</t>
-  </si>
-  <si>
-    <t>Universidade do Porto</t>
-  </si>
-  <si>
-    <t>Universitair Ziekenhuis Brussel</t>
-  </si>
-  <si>
-    <t>Universitair Ziekenhuis Leuven</t>
-  </si>
-  <si>
-    <t>University Clinic of Pulmonary and Allergic Diseases Golnik</t>
-  </si>
-  <si>
-    <t>University College London</t>
-  </si>
-  <si>
-    <t>University Hospital Bonn</t>
-  </si>
-  <si>
-    <t>University Hospital Brno</t>
-  </si>
-  <si>
-    <t>University Hospital Centre Zagreb</t>
+    <t>University Hospital Heidelberg</t>
   </si>
   <si>
     <t>University Hospital in Motol</t>
   </si>
   <si>
-    <t>University Hospital Kralovske Vinohrady</t>
-  </si>
-  <si>
-    <t>University Hospital Magdeburg</t>
-  </si>
-  <si>
-    <t>University Hospital Münster</t>
-  </si>
-  <si>
-    <t>University Hospital of Geneva</t>
-  </si>
-  <si>
-    <t>University Hospital Regensburg</t>
-  </si>
-  <si>
-    <t>University Hospital Schleswig-Holstein</t>
-  </si>
-  <si>
-    <t>University Medical Center Freiburg</t>
-  </si>
-  <si>
     <t>University Medical Center Groningen</t>
   </si>
   <si>
-    <t>University Medical Center Hamburg-Eppendorf</t>
-  </si>
-  <si>
-    <t>University Medical Center Utrecht</t>
-  </si>
-  <si>
-    <t>University of Brescia</t>
-  </si>
-  <si>
-    <t>University of Bristol</t>
-  </si>
-  <si>
-    <t>University of British Columbia</t>
+    <t>University of Antwerp</t>
   </si>
   <si>
     <t>University of Cambridge</t>
   </si>
   <si>
-    <t>University of Catania</t>
-  </si>
-  <si>
-    <t>University of Coimbra</t>
-  </si>
-  <si>
-    <t>University of Copenhagen</t>
+    <t>University of Campania "Luigi Vanvitelli"</t>
   </si>
   <si>
     <t>University of Crete</t>
   </si>
   <si>
-    <t>University of Debrecen</t>
-  </si>
-  <si>
-    <t>University of Dundee</t>
-  </si>
-  <si>
-    <t>University of Eastern Finland</t>
-  </si>
-  <si>
-    <t>University of Ferrara</t>
-  </si>
-  <si>
     <t>University of Groningen</t>
   </si>
   <si>
-    <t>University of KwaZulu-Natal</t>
+    <t>University of Lübeck</t>
   </si>
   <si>
-    <t>University of Liège</t>
+    <t>University of Otago</t>
   </si>
   <si>
-    <t>University of Messina</t>
+    <t>University of Siena</t>
   </si>
   <si>
-    <t>University of Münster</t>
-  </si>
-  <si>
-    <t>University of Oslo</t>
-  </si>
-  <si>
-    <t>University of Oulu</t>
-  </si>
-  <si>
-    <t>University of Oxford</t>
-  </si>
-  <si>
-    <t>University of Pecs</t>
-  </si>
-  <si>
-    <t>University of Rome Tor Vergata</t>
-  </si>
-  <si>
-    <t>University of Salzburg</t>
-  </si>
-  <si>
-    <t>University of Southampton</t>
-  </si>
-  <si>
-    <t>University of Southern Denmark</t>
-  </si>
-  <si>
-    <t>University of Surrey</t>
-  </si>
-  <si>
-    <t>University of Szeged</t>
-  </si>
-  <si>
-    <t>University of Turin</t>
-  </si>
-  <si>
-    <t>University of Twente</t>
+    <t>University of Tartu</t>
   </si>
   <si>
     <t>University of Tübingen</t>
   </si>
   <si>
-    <t>University of Ulster</t>
+    <t>uoc-zaganas</t>
   </si>
   <si>
-    <t>University of Warmia and Mazury in Olsztyn</t>
+    <t>uzg-poppe</t>
   </si>
   <si>
-    <t>Universität Innsbruck</t>
+    <t>uzl-vermeesch</t>
   </si>
   <si>
-    <t>Universitätsklinikum Erlangen</t>
-  </si>
-  <si>
-    <t>Universitätsklinikum Tübingen</t>
-  </si>
-  <si>
-    <t>Universitätsklinikum Würzburg</t>
-  </si>
-  <si>
-    <t>Universitätsmedizin Göttingen</t>
-  </si>
-  <si>
-    <t>Universitätsmedizin Rostock</t>
-  </si>
-  <si>
-    <t>Université de Bordeaux</t>
-  </si>
-  <si>
-    <t>Université de Rouen Normandie</t>
-  </si>
-  <si>
-    <t>Uniwersytecki Szpital Kliniczny w Olsztynie</t>
-  </si>
-  <si>
-    <t>Uppsala University</t>
-  </si>
-  <si>
-    <t>Uppsala University Hospital</t>
-  </si>
-  <si>
-    <t>Utrecht University</t>
-  </si>
-  <si>
-    <t>Vall d'Hebron Hospital Universitari</t>
+    <t>uzlu-lohmann</t>
   </si>
   <si>
     <t>Vall d'Hebron Institut de Recerca</t>
   </si>
   <si>
-    <t>Vall d'Hebron Institute of Oncology</t>
+    <t>VASCERN</t>
   </si>
   <si>
-    <t>Varsinais-Suomen Sairaanhoitopiiri</t>
+    <t>VIB-UAntwerp Center for Molecular Neurology</t>
   </si>
   <si>
-    <t>Verslavingszorg Noord Nederland</t>
-  </si>
-  <si>
-    <t>Victor Babeș University of Medicine and Pharmacy Timișoara</t>
+    <t>vibua-weckhuysen</t>
   </si>
   <si>
     <t>Vilnius University Hospital Santariskiu Klinikos</t>
   </si>
   <si>
-    <t>Vrije Universiteit Amsterdam</t>
-  </si>
-  <si>
-    <t>Vrije Universiteit Brussel</t>
-  </si>
-  <si>
-    <t>Vytautas Magnus University</t>
-  </si>
-  <si>
-    <t>Wilhelmina Children's Hospital</t>
-  </si>
-  <si>
-    <t>Zealand University Hospital</t>
-  </si>
-  <si>
-    <t>Ziekenhuis Groep Twente</t>
-  </si>
-  <si>
-    <t>Ziekenhuis Nij Smellinghe</t>
-  </si>
-  <si>
-    <t>ZorgSaam</t>
-  </si>
-  <si>
-    <t>Zuyderland Medisch Centrum</t>
-  </si>
-  <si>
-    <t>Örebro University</t>
+    <t>vuhsk-ambrozaityte</t>
   </si>
   <si>
     <t>Checksum type</t>
@@ -6837,5995 +6078,5995 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2997">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C7</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000009000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000011000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000012000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C20</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000013000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000014000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C22</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000015000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C23</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000016000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000017000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000018000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000019000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C28</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C29</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C30</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C33</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000020000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000021000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C35</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000022000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C36</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000023000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000024000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C38</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000025000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C39</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000026000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000027000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000028000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C42</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000029000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C45</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C46</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C48</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C49</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000030000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000031000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000032000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C52</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000033000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000034000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C54</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000035000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000036000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000037000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000038000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C58</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000039000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C59</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C60</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C62</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C63</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C65</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000040000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C66</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000041000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C67</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000042000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000043000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000044000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C70</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000045000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000046000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C72</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000047000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C73</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000048000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C74</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000049000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C75</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C76</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C78</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C79</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C80</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C81</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000050000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C82</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000051000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000052000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000053000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000054000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C86</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000055000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C87</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000056000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C88</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000057000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C89</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000058000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C90</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000059000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C91</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C92</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C93</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C94</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C95</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C96</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C97</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000060000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C98</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000061000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C99</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000062000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000063000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000064000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C102</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000065000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C103</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000066000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C104</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000067000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C105</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000068000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C106</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000069000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C107</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C108</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C109</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C111</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C113</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000070000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C114</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000071000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C115</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000072000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C116</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000073000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C117</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000074000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C118</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000075000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C119</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000076000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C120</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000077000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000078000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C122</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000079000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C127</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C128</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C129</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000080000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000081000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000082000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000083000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000084000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C134</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000085000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C135</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000086000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C136</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000087000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C137</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000088000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C138</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000089000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C139</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C140</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C141</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C142</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C143</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C144</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C145</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000090000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C146</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000091000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C147</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000092000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C148</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000093000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C149</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000094000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C150</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000095000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C151</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000096000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C152</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000097000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C153</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000098000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C154</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000099000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C155</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009A000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C156</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009B000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C157</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009C000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C158</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009D000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C159</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009E000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C160</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009F000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C161</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A0000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C162</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A1000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C163</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A2000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C164</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A3000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A4000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C166</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A5000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C167</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A6000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C168</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A7000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C169</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A8000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C170</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A9000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C171</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AA000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C172</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AB000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C173</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AC000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C174</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AD000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C175</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AE000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C176</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AF000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C177</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B0000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C178</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B1000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C179</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B2000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C180</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B3000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C181</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B4000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C182</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B5000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C183</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B6000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C184</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B7000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C185</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B8000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C186</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B9000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C187</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BA000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C188</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BB000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C189</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BC000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C190</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BD000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C191</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BE000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C192</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BF000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C193</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C0000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C194</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C1000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C195</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C2000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C196</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C3000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C197</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C4000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C198</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C5000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C199</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C6000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C200</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C7000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C201</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C8000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C202</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C9000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C203</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CA000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C204</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CB000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C205</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CC000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C206</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CD000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C207</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CE000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C208</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CF000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C209</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D0000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C210</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D1000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C211</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D2000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C212</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D3000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C213</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D4000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C214</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D5000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C215</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D6000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C216</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D7000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C217</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D8000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C218</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D9000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C219</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DA000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C220</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DB000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C221</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DC000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C222</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DD000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C223</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DE000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C224</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DF000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C225</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E0000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C226</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E1000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C227</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E2000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C228</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E3000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C229</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E4000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C230</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E5000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C231</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E6000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C232</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E7000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C233</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E8000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C234</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E9000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C235</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EA000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C236</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EB000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C237</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EC000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C238</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000ED000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C239</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EE000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C240</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EF000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C241</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F0000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C242</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F1000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C243</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F2000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C244</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F3000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C245</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F4000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C246</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F5000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C247</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F6000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C248</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F7000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C249</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F8000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C250</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F9000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C251</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FA000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C252</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FB000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C253</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FC000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C254</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FD000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C255</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FE000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C256</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FF000000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C257</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C258</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C259</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C260</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C261</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C262</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C263</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C264</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C265</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C266</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000009010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C267</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C268</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C269</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C270</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C271</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C272</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C273</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C274</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000011010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C275</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000012010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C276</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000013010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C277</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000014010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C278</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000015010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C279</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000016010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C280</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000017010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C281</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000018010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C282</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000019010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C283</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C284</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C285</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C286</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C287</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C288</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C289</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000020010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C290</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000021010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C291</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000022010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C292</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000023010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C293</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000024010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C294</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000025010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C295</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000026010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C296</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000027010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C297</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000028010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C298</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000029010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C299</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C300</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C301</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C302</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C303</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C304</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C305</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000030010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C306</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000031010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C307</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000032010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C308</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000033010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C309</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000034010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C310</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000035010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C311</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000036010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C312</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000037010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C313</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000038010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C314</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000039010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C315</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C316</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C317</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C318</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C319</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C320</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C321</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000040010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C322</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000041010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C323</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000042010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C324</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000043010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C325</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000044010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C326</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000045010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C327</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000046010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C328</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000047010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C329</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000048010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C330</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000049010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C331</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C332</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C333</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C334</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C335</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C336</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C337</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000050010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C338</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000051010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C339</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000052010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C340</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000053010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C341</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000054010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C342</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000055010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C343</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000056010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C344</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000057010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C345</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000058010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C346</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000059010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C347</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C348</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C349</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C350</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C351</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C352</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C353</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000060010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C354</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000061010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C355</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000062010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C356</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000063010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C357</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000064010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C358</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000065010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C359</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000066010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C360</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000067010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C361</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000068010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C362</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000069010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C363</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C364</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C365</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C366</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C367</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C368</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C369</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000070010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C370</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000071010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C371</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000072010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C372</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000073010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C373</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000074010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C374</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000075010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C375</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000076010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C376</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000077010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C377</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000078010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C378</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000079010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C379</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C380</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C381</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C382</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C383</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C384</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C385</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000080010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C386</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000081010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C387</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000082010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C388</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000083010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C389</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000084010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C390</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000085010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C391</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000086010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C392</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000087010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C393</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000088010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C394</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000089010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C395</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C396</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C397</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C398</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C399</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C400</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C401</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000090010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C402</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000091010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C403</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000092010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C404</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000093010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C405</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000094010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C406</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000095010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C407</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000096010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C408</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000097010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C409</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000098010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C410</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000099010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C411</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009A010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C412</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009B010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C413</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009C010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C414</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009D010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C415</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009E010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C416</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009F010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C417</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A0010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C418</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A1010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C419</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A2010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C420</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A3010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C421</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A4010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C422</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A5010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C423</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A6010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C424</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A7010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C425</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A8010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C426</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A9010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C427</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AA010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C428</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AB010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C429</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AC010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C430</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AD010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C431</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AE010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C432</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AF010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C433</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B0010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C434</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B1010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C435</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B2010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C436</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B3010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C437</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B4010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C438</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B5010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C439</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B6010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C440</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B7010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C441</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B8010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C442</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B9010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C443</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BA010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C444</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BB010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C445</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BC010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C446</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BD010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C447</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BE010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C448</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BF010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C449</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C0010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C450</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C1010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C451</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C2010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C452</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C3010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C453</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C4010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C454</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C5010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C455</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C6010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C456</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C7010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C457</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C8010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C458</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C9010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C459</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CA010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C460</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CB010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C461</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CC010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C462</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CD010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C463</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CE010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C464</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CF010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C465</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D0010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C466</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D1010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C467</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D2010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C468</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D3010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C469</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D4010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C470</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D5010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C471</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D6010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C472</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D7010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C473</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D8010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C474</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D9010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C475</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DA010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C476</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DB010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C477</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DC010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C478</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DD010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C479</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DE010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C480</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DF010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C481</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E0010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C482</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E1010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C483</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E2010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C484</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E3010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C485</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E4010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C486</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E5010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C487</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E6010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C488</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E7010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C489</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E8010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C490</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E9010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C491</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EA010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C492</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EB010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C493</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EC010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C494</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000ED010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C495</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EE010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C496</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EF010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C497</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F0010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C498</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F1010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F2010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F3010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F4010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C502</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F5010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C503</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F6010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C504</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F7010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C505</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F8010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C506</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F9010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C507</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FA010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C508</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FB010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C509</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FC010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C510</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FD010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C511</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FE010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C512</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FF010000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C513</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C514</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C515</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C516</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C517</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C518</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C519</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C520</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C521</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C522</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000009020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C523</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C524</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C525</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C526</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C527</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C528</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C529</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C530</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000011020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C531</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000012020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C532</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000013020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C533</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000014020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C534</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000015020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C535</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000016020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C536</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000017020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C537</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000018020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C538</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000019020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C539</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C540</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C541</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C542</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C543</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C544</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C545</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000020020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C546</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000021020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C547</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000022020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C548</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000023020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C549</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000024020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C550</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000025020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C551</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000026020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C552</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000027020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C553</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000028020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C554</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000029020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C555</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C556</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C557</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C558</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C559</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C560</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C561</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000030020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C562</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000031020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C563</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000032020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C564</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000033020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C565</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000034020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C566</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000035020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C567</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000036020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C568</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000037020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C569</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000038020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C570</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000039020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C571</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C572</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C573</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C574</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C575</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C577</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000040020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C578</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000041020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C579</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000042020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C580</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000043020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C581</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000044020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C582</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000045020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C583</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000046020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C584</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000047020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C585</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000048020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C586</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000049020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C587</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C588</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C589</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C590</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C591</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C592</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C593</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000050020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C594</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000051020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C595</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000052020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C596</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000053020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C597</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000054020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C598</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000055020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C599</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000056020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C600</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000057020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C601</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000058020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C602</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000059020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C603</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C604</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C605</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C606</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C607</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C608</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C609</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000060020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C610</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000061020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C611</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000062020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C612</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000063020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C613</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000064020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C614</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000065020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C615</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000066020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C616</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000067020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C617</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000068020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C618</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000069020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C619</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C620</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C621</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C622</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C623</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C624</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C625</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000070020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C626</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000071020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C627</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000072020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C628</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000073020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C629</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000074020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C630</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000075020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C631</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000076020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C632</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000077020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C633</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000078020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C634</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000079020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C635</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C636</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C637</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C638</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C639</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C640</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C641</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000080020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C642</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000081020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C643</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000082020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C644</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000083020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C645</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000084020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C646</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000085020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C647</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000086020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C648</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000087020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C649</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000088020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C650</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000089020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C651</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C652</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C653</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C654</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C655</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C656</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C657</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000090020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C658</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000091020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C659</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000092020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C660</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000093020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C661</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000094020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C662</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000095020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C663</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000096020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C664</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000097020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C665</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000098020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C666</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000099020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C667</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009A020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C668</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009B020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C669</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009C020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C670</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009D020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C671</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009E020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C672</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009F020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C673</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A0020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C674</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A1020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C675</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A2020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C676</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A3020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C677</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A4020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C678</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A5020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C679</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A6020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C680</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A7020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C681</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A8020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C682</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A9020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C683</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AA020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C684</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AB020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C685</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AC020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C686</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AD020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C687</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AE020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C688</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AF020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C689</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B0020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C690</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B1020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C691</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B2020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C692</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B3020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C693</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B4020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C694</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B5020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C695</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B6020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C696</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B7020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C697</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B8020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C698</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B9020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C699</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BA020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C700</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BB020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BC020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C702</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BD020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C703</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BE020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C704</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BF020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C705</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C0020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C706</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C1020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C707</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C2020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C708</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C3020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C709</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C4020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C710</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C5020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C711</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C6020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C712</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C7020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C713</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C8020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C714</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C9020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C715</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CA020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C716</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CB020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C717</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CC020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C718</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CD020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C719</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CE020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C720</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CF020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C721</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D0020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C722</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D1020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C723</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D2020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C724</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D3020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C725</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D4020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C726</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D5020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C727</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D6020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C728</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D7020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C729</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D8020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C730</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D9020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C731</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DA020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C732</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DB020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C733</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DC020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C734</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DD020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C735</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DE020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C736</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DF020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C737</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E0020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C738</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E1020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C739</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E2020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C740</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E3020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C741</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E4020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C742</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E5020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C743</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E6020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C744</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E7020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C745</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E8020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C746</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E9020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C747</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EA020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C748</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EB020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C749</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EC020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C750</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000ED020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C751</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EE020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C752</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000EF020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C753</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F0020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C754</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F1020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C755</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F2020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C756</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F3020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C757</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F4020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C758</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F5020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C759</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F6020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C760</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F7020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C761</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F8020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C762</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000F9020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C763</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FA020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C764</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FB020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C765</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FC020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C766</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FD020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C767</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FE020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C768</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000FF020000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C769</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C770</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C771</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C772</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C773</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C774</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C775</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C776</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C777</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C778</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000009030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C779</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C780</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C781</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C782</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C783</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C784</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C785</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C786</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000011030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C787</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000012030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C788</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000013030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C789</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000014030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C790</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000015030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C791</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000016030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C792</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000017030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C793</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000018030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C794</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000019030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C795</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C796</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C797</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C798</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C799</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C800</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C801</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000020030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C802</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000021030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C803</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000022030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C804</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000023030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C805</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000024030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C806</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000025030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C807</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000026030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C808</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000027030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C809</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000028030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C810</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000029030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C811</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C812</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C813</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C814</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C815</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C816</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00002F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C817</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000030030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C818</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000031030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C819</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000032030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C820</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000033030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C821</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000034030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C822</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000035030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C823</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000036030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C824</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000037030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C825</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000038030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C826</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000039030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C827</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C828</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C829</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C830</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C831</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C832</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00003F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C833</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000040030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C834</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000041030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C835</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000042030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C836</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000043030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C837</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000044030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C838</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000045030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C839</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000046030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C840</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000047030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C841</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000048030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C842</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000049030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C843</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C844</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C845</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C846</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C847</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C848</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00004F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C849</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000050030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C850</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000051030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C851</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000052030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C852</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000053030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C853</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000054030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C854</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000055030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C855</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000056030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C856</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000057030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C857</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000058030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C858</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000059030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C859</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C860</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C861</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C862</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C863</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C864</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00005F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C865</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000060030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C866</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000061030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C867</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000062030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C868</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000063030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C869</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000064030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C870</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000065030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C871</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000066030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C872</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000067030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C873</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000068030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C874</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000069030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C875</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C876</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C877</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C878</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C879</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C880</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00006F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C881</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000070030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C882</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000071030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C883</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000072030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C884</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000073030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C885</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000074030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C886</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000075030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C887</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000076030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C888</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000077030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C889</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000078030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C890</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000079030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C891</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C892</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C893</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C894</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C895</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C896</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00007F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C897</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000080030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C898</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000081030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C899</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000082030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C900</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000083030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C901</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000084030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C902</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000085030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C903</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000086030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C904</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000087030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C905</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000088030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C906</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000089030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C907</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C908</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C909</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C910</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C911</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C912</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00008F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C913</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000090030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C914</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000091030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C915</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000092030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C916</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000093030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C917</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000094030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C918</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000095030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C919</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000096030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C920</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000097030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C921</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000098030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C922</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000099030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C923</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009A030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C924</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009B030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C925</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009C030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C926</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009D030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C927</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009E030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C928</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00009F030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C929</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A0030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C930</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A1030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C931</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A2030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C932</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A3030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C933</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A4030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C934</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A5030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C935</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A6030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C936</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A7030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C937</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A8030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C938</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000A9030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C939</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AA030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C940</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AB030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C941</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AC030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C942</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AD030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C943</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AE030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C944</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000AF030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C945</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B0030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C946</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B1030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C947</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B2030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C948</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B3030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C949</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B4030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C950</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B5030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C951</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B6030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C952</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B7030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C953</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B8030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C954</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000B9030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C955</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BA030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C956</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BB030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C957</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BC030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C958</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BD030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C959</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BE030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C960</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000BF030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C961</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C0030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C962</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C1030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C963</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C2030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C964</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C3030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C965</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C4030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C966</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C5030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C967</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C6030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C968</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C7030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C969</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C8030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C970</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000C9030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C971</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CA030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C972</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CB030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C973</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CC030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C974</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CD030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C975</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CE030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C976</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000CF030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C977</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D0030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C978</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D1030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C979</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D2030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C980</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D3030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C981</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D4030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C982</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D5030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C983</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D6030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C984</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D7030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C985</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D8030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000D9030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C987</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DA030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C988</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DB030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C989</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DC030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C990</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DD030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C991</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DE030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C992</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000DF030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C993</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E0030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C994</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E1030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C995</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E2030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C996</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E3030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C997</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E4030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C998</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E5030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C999</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-0000E6030000}">
           <x14:formula1>
-            <xm:f>lookups!A2:A334</xm:f>
+            <xm:f>lookups!A2:A108</xm:f>
           </x14:formula1>
           <xm:sqref>C1000</xm:sqref>
         </x14:dataValidation>
@@ -24825,10 +24066,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C334"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="85.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -24838,10 +24079,10 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>346</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -24849,10 +24090,10 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>347</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -24860,10 +24101,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>344</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>348</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -24871,10 +24112,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>345</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -24882,7 +24123,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -24890,7 +24131,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -24898,7 +24139,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>352</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -24906,7 +24147,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>353</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -24914,7 +24155,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -24922,7 +24163,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>355</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -24930,7 +24171,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -24938,7 +24179,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -24946,7 +24187,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>358</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -24954,7 +24195,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>359</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -25425,1136 +24666,6 @@
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A172" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A176" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A190" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A193" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A194" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A195" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A196" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A197" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A199" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A200" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A201" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A202" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A203" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A205" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A206" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A207" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A208" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A209" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A210" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A211" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A212" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A213" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A214" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A215" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A216" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A217" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A219" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A220" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A221" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A222" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A223" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A225" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A226" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A227" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A228" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A229" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A230" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A231" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A232" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A233" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A234" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A235" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A236" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A237" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A238" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A239" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A240" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A241" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A242" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A243" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A244" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A245" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A246" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A247" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A248" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A249" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A250" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A251" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A252" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A253" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A254" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A255" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A256" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A257" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A258" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A259" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A260" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A261" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A262" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A263" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A264" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A265" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A266" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A267" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A268" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A269" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A270" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A271" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A272" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A273" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A274" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A275" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A276" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A277" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A279" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A280" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A281" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A282" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A283" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A284" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A285" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A286" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A287" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A288" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A289" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A290" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A291" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A292" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A293" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A294" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A295" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A296" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A297" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A298" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A299" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A300" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A301" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A302" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A304" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A305" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A307" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A308" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A309" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A311" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A312" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A313" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A314" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A315" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A316" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A317" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A318" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A319" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A320" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A321" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A322" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A323" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A324" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A325" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A326" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A327" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A328" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A329" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A330" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A331" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A332" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A333" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A334" t="s">
-        <v>341</v>
       </c>
     </row>
   </sheetData>
